--- a/content/Lectures/Semester 1/Week 07 - Flow Shop and Job Shop Scheduling/2 Lecture Demos/2 Johnsons rule in Excel.xlsx
+++ b/content/Lectures/Semester 1/Week 07 - Flow Shop and Job Shop Scheduling/2 Lecture Demos/2 Johnsons rule in Excel.xlsx
@@ -16186,10 +16186,10 @@
         <v>5</v>
       </c>
       <c r="U64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V64" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="V64" s="3" t="s">
-        <v>2</v>
       </c>
       <c r="W64" s="3" t="s">
         <v>1</v>
@@ -16213,10 +16213,10 @@
         <v>7</v>
       </c>
       <c r="U65" s="3">
+        <v>7</v>
+      </c>
+      <c r="V65" s="3">
         <v>6</v>
-      </c>
-      <c r="V65" s="3">
-        <v>7</v>
       </c>
       <c r="W65" s="3">
         <v>8</v>
@@ -16240,15 +16240,15 @@
       </c>
       <c r="AC65" s="18">
         <f>U65</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD65" s="21">
         <f>AB65+AC65</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE65" s="18">
         <f>V65</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF65" s="21">
         <f>AD65+AE65</f>
@@ -16275,7 +16275,7 @@
       <c r="AB66" s="21"/>
       <c r="AC66" s="21">
         <f>AB65+AC65</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD66" s="21"/>
       <c r="AE66" s="21">
@@ -16297,10 +16297,10 @@
         <v>4</v>
       </c>
       <c r="U67" s="3">
+        <v>5</v>
+      </c>
+      <c r="V67" s="3">
         <v>9</v>
-      </c>
-      <c r="V67" s="3">
-        <v>5</v>
       </c>
       <c r="W67" s="3">
         <v>11</v>
@@ -16324,19 +16324,19 @@
       </c>
       <c r="AC67" s="18">
         <f>U67</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AD67" s="21">
         <f>AC67+MAX(AB67,AC66)</f>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE67" s="18">
         <f>V67</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AF67" s="21">
         <f>AE67+MAX(AD67,AE66)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AG67" s="18">
         <f>W67</f>
@@ -16359,17 +16359,17 @@
       <c r="AB68" s="21"/>
       <c r="AC68" s="21">
         <f>AC67+MAX(AB67,AC66)</f>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AD68" s="21"/>
       <c r="AE68" s="21">
         <f>AE67+MAX(AD67,AE66)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AF68" s="21"/>
       <c r="AG68" s="21">
         <f>AG67+MAX(AF67,AG66)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH68" s="21"/>
     </row>
@@ -16381,10 +16381,10 @@
         <v>2</v>
       </c>
       <c r="U69" s="3">
+        <v>8</v>
+      </c>
+      <c r="V69" s="3">
         <v>9</v>
-      </c>
-      <c r="V69" s="3">
-        <v>8</v>
       </c>
       <c r="W69" s="3">
         <v>3</v>
@@ -16408,19 +16408,19 @@
       </c>
       <c r="AC69" s="18">
         <f>U69</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD69" s="21">
         <f>AC69+MAX(AB69,AC68)</f>
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="AE69" s="18">
         <f>V69</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF69" s="21">
         <f>AE69+MAX(AD69,AE68)</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AG69" s="18">
         <f>W69</f>
@@ -16443,17 +16443,17 @@
       <c r="AB70" s="21"/>
       <c r="AC70" s="21">
         <f>AC69+MAX(AB69,AC68)</f>
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="AD70" s="21"/>
       <c r="AE70" s="21">
         <f>AE69+MAX(AD69,AE68)</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF70" s="21"/>
       <c r="AG70" s="21">
         <f>AG69+MAX(AF69,AG68)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AH70" s="21"/>
     </row>
@@ -16465,10 +16465,10 @@
         <v>12</v>
       </c>
       <c r="U71" s="3">
+        <v>5</v>
+      </c>
+      <c r="V71" s="3">
         <v>14</v>
-      </c>
-      <c r="V71" s="3">
-        <v>5</v>
       </c>
       <c r="W71" s="3">
         <v>3</v>
@@ -16492,19 +16492,19 @@
       </c>
       <c r="AC71" s="18">
         <f>U71</f>
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AD71" s="21">
         <f>AC71+MAX(AB71,AC70)</f>
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="AE71" s="18">
         <f>V71</f>
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AF71" s="21">
         <f>AE71+MAX(AD71,AE70)</f>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AG71" s="18">
         <f>W71</f>
@@ -16527,17 +16527,17 @@
       <c r="AB72" s="2"/>
       <c r="AC72" s="21">
         <f>AC71+MAX(AB71,AC70)</f>
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="AD72" s="2"/>
       <c r="AE72" s="21">
         <f>AE71+MAX(AD71,AE70)</f>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AF72" s="2"/>
       <c r="AG72" s="21">
         <f>AG71+MAX(AF71,AG70)</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AH72" s="2"/>
     </row>
@@ -16549,10 +16549,10 @@
         <v>3</v>
       </c>
       <c r="U73" s="3">
+        <v>9</v>
+      </c>
+      <c r="V73" s="3">
         <v>2</v>
-      </c>
-      <c r="V73" s="3">
-        <v>9</v>
       </c>
       <c r="W73" s="3">
         <v>11</v>
@@ -16576,19 +16576,19 @@
       </c>
       <c r="AC73" s="18">
         <f>U73</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AD73" s="21">
         <f>AC73+MAX(AB73,AC72)</f>
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="AE73" s="18">
         <f>V73</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AF73" s="21">
         <f>AE73+MAX(AD73,AE72)</f>
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="AG73" s="18">
         <f>W73</f>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="AH73" s="21">
         <f>AG73+MAX(AF73,AG72)</f>
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="18:34" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -16608,10 +16608,10 @@
         <v>5</v>
       </c>
       <c r="U77" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="V77" s="31" t="s">
         <v>4</v>
-      </c>
-      <c r="V77" s="31" t="s">
-        <v>2</v>
       </c>
       <c r="W77" s="31" t="s">
         <v>1</v>
@@ -16625,10 +16625,10 @@
         <v>7</v>
       </c>
       <c r="U78" s="31">
+        <v>7</v>
+      </c>
+      <c r="V78" s="31">
         <v>6</v>
-      </c>
-      <c r="V78" s="31">
-        <v>7</v>
       </c>
       <c r="W78" s="31">
         <v>8</v>
@@ -16642,10 +16642,10 @@
         <v>4</v>
       </c>
       <c r="U79" s="31">
+        <v>5</v>
+      </c>
+      <c r="V79" s="31">
         <v>9</v>
-      </c>
-      <c r="V79" s="31">
-        <v>5</v>
       </c>
       <c r="W79" s="31">
         <v>11</v>
@@ -16659,10 +16659,10 @@
         <v>2</v>
       </c>
       <c r="U80" s="31">
+        <v>8</v>
+      </c>
+      <c r="V80" s="31">
         <v>9</v>
-      </c>
-      <c r="V80" s="31">
-        <v>8</v>
       </c>
       <c r="W80" s="31">
         <v>3</v>
@@ -16676,10 +16676,10 @@
         <v>12</v>
       </c>
       <c r="U81" s="31">
+        <v>5</v>
+      </c>
+      <c r="V81" s="31">
         <v>14</v>
-      </c>
-      <c r="V81" s="31">
-        <v>5</v>
       </c>
       <c r="W81" s="31">
         <v>3</v>
@@ -16693,10 +16693,10 @@
         <v>3</v>
       </c>
       <c r="U82" s="31">
+        <v>9</v>
+      </c>
+      <c r="V82" s="31">
         <v>2</v>
-      </c>
-      <c r="V82" s="31">
-        <v>9</v>
       </c>
       <c r="W82" s="31">
         <v>11</v>
